--- a/assets/app_hyup/excel/S_estimate_excel.xlsx
+++ b/assets/app_hyup/excel/S_estimate_excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/574bf504d400291e/문서/카카오톡 받은 파일/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\jmtech\assets\app_hyup\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{206F775A-57E0-472B-95E1-D1EBF29E753B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9A3C48C-DC01-4754-949B-5CB8CB4D8317}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BA776B-6031-4A98-BE11-9C6CE7EC9E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A8E3B584-EFA5-47FD-B92C-1698FC3C9E4C}"/>
+    <workbookView xWindow="7605" yWindow="930" windowWidth="21600" windowHeight="11295" xr2:uid="{A8E3B584-EFA5-47FD-B92C-1698FC3C9E4C}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
   <numFmts count="1">
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1268,6 +1268,270 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="21" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="42" fontId="21" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="42" fontId="21" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="42" fontId="21" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="42" fontId="20" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="42" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="42" fontId="21" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1277,15 +1541,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="42" fontId="20" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1312,261 +1567,6 @@
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1697,6 +1697,67 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>86591</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>121227</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>33515</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>34633</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6DE418E-3953-4BDE-8CD2-FB741C2EF2B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="14755091" y="1939636"/>
+          <a:ext cx="864788" cy="623452"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1705,9 +1766,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1745,7 +1806,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1851,7 +1912,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1993,7 +2054,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2005,7 +2066,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:W43"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="4" width="11.625" customWidth="1"/>
     <col min="5" max="5" width="42" bestFit="1" customWidth="1"/>
@@ -2020,77 +2081,77 @@
     <col min="21" max="21" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:22">
-      <c r="C2" s="121" t="s">
+    <row r="2" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="121"/>
-      <c r="P2" s="121"/>
-      <c r="Q2" s="121"/>
-      <c r="R2" s="121"/>
-      <c r="S2" s="121"/>
-      <c r="T2" s="121"/>
-      <c r="U2" s="121"/>
-    </row>
-    <row r="3" spans="3:22">
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="121"/>
-      <c r="Q3" s="121"/>
-      <c r="R3" s="121"/>
-      <c r="S3" s="121"/>
-      <c r="T3" s="121"/>
-      <c r="U3" s="121"/>
-    </row>
-    <row r="4" spans="3:22" ht="48" customHeight="1">
-      <c r="C4" s="121"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="121"/>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121"/>
-      <c r="S4" s="121"/>
-      <c r="T4" s="121"/>
-      <c r="U4" s="121"/>
-    </row>
-    <row r="5" spans="3:22" ht="21" thickBot="1">
-      <c r="C5" s="80" t="s">
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+    </row>
+    <row r="3" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+    </row>
+    <row r="4" spans="3:22" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+    </row>
+    <row r="5" spans="3:22" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
@@ -2101,230 +2162,230 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="12"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-    </row>
-    <row r="6" spans="3:22" ht="26.25" customHeight="1">
-      <c r="C6" s="81" t="s">
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="63"/>
+      <c r="S5" s="63"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="63"/>
+    </row>
+    <row r="6" spans="3:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="54" t="s">
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="47" t="s">
+      <c r="I6" s="101"/>
+      <c r="J6" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="49"/>
-    </row>
-    <row r="7" spans="3:22" ht="17.25" customHeight="1">
-      <c r="C7" s="84"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="52"/>
-    </row>
-    <row r="8" spans="3:22" ht="38.25" customHeight="1">
-      <c r="C8" s="77"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="58" t="s">
+      <c r="K6" s="107"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="107"/>
+      <c r="O6" s="107"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="108"/>
+      <c r="S6" s="108"/>
+      <c r="T6" s="108"/>
+      <c r="U6" s="109"/>
+    </row>
+    <row r="7" spans="3:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="80"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="111"/>
+      <c r="Q7" s="111"/>
+      <c r="R7" s="111"/>
+      <c r="S7" s="111"/>
+      <c r="T7" s="111"/>
+      <c r="U7" s="112"/>
+    </row>
+    <row r="8" spans="3:22" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="73"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="58"/>
-      <c r="J8" s="53" t="s">
+      <c r="I8" s="102"/>
+      <c r="J8" s="113" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="53"/>
-      <c r="L8" s="58" t="s">
+      <c r="K8" s="113"/>
+      <c r="L8" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="71" t="s">
+      <c r="M8" s="102"/>
+      <c r="N8" s="102"/>
+      <c r="O8" s="102"/>
+      <c r="P8" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="73"/>
-    </row>
-    <row r="9" spans="3:22" ht="26.25" customHeight="1">
-      <c r="C9" s="87" t="s">
+      <c r="Q8" s="68"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="68"/>
+      <c r="T8" s="68"/>
+      <c r="U8" s="69"/>
+    </row>
+    <row r="9" spans="3:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="58" t="s">
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="102" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="58"/>
-      <c r="J9" s="50" t="s">
+      <c r="I9" s="102"/>
+      <c r="J9" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="52"/>
-    </row>
-    <row r="10" spans="3:22" ht="17.25" customHeight="1">
-      <c r="C10" s="87"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="51"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="52"/>
-    </row>
-    <row r="11" spans="3:22" ht="45.75" customHeight="1">
-      <c r="C11" s="77" t="s">
+      <c r="K9" s="110"/>
+      <c r="L9" s="110"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="110"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="111"/>
+      <c r="R9" s="111"/>
+      <c r="S9" s="111"/>
+      <c r="T9" s="111"/>
+      <c r="U9" s="112"/>
+    </row>
+    <row r="10" spans="3:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="83"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="111"/>
+      <c r="S10" s="111"/>
+      <c r="T10" s="111"/>
+      <c r="U10" s="112"/>
+    </row>
+    <row r="11" spans="3:22" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="58" t="s">
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="58"/>
-      <c r="J11" s="53" t="s">
+      <c r="I11" s="102"/>
+      <c r="J11" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="53"/>
-      <c r="L11" s="58" t="s">
+      <c r="K11" s="113"/>
+      <c r="L11" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="M11" s="58"/>
-      <c r="N11" s="58"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="71" t="s">
+      <c r="M11" s="102"/>
+      <c r="N11" s="102"/>
+      <c r="O11" s="102"/>
+      <c r="P11" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="73"/>
-    </row>
-    <row r="12" spans="3:22" ht="34.5" customHeight="1" thickBot="1">
-      <c r="C12" s="91"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="59" t="s">
+      <c r="Q11" s="68"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="68"/>
+      <c r="T11" s="68"/>
+      <c r="U11" s="69"/>
+    </row>
+    <row r="12" spans="3:22" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="89"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="59"/>
-      <c r="J12" s="94" t="s">
+      <c r="I12" s="93"/>
+      <c r="J12" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="94"/>
-      <c r="L12" s="59" t="s">
+      <c r="K12" s="92"/>
+      <c r="L12" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="M12" s="59"/>
-      <c r="N12" s="59"/>
-      <c r="O12" s="59"/>
-      <c r="P12" s="74" t="s">
+      <c r="M12" s="93"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
+      <c r="P12" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="75"/>
-      <c r="S12" s="75"/>
-      <c r="T12" s="75"/>
-      <c r="U12" s="76"/>
-    </row>
-    <row r="13" spans="3:22" ht="44.25" customHeight="1" thickBot="1">
-      <c r="C13" s="26" t="str">
+      <c r="Q12" s="71"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="71"/>
+      <c r="T12" s="71"/>
+      <c r="U12" s="72"/>
+    </row>
+    <row r="13" spans="3:22" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="114" t="str">
         <f>" 합계금액 : 일금 "      &amp; NUMBERSTRING(K43,1) &amp;"원정      (" &amp; DOLLAR(K43) &amp; ")"   &amp;"  (부가세 포함)"</f>
         <v xml:space="preserve"> 합계금액 : 일금 영원정      (₩0)  (부가세 포함)</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="28"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="115"/>
+      <c r="L13" s="115"/>
+      <c r="M13" s="115"/>
+      <c r="N13" s="115"/>
+      <c r="O13" s="115"/>
+      <c r="P13" s="115"/>
+      <c r="Q13" s="115"/>
+      <c r="R13" s="115"/>
+      <c r="S13" s="115"/>
+      <c r="T13" s="115"/>
+      <c r="U13" s="116"/>
       <c r="V13" s="16"/>
     </row>
-    <row r="14" spans="3:22" ht="34.5" customHeight="1">
-      <c r="C14" s="66" t="s">
+    <row r="14" spans="3:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="67"/>
+      <c r="D14" s="65"/>
       <c r="E14" s="17" t="s">
         <v>12</v>
       </c>
@@ -2334,553 +2395,553 @@
       <c r="G14" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H14" s="60" t="s">
+      <c r="H14" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="90"/>
-      <c r="J14" s="60" t="s">
+      <c r="I14" s="87"/>
+      <c r="J14" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="61"/>
-      <c r="L14" s="68" t="s">
+      <c r="K14" s="103"/>
+      <c r="L14" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="M14" s="69"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="68" t="s">
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="Q14" s="69"/>
-      <c r="R14" s="69"/>
-      <c r="S14" s="69"/>
-      <c r="T14" s="69"/>
-      <c r="U14" s="120"/>
-    </row>
-    <row r="15" spans="3:22" ht="33" customHeight="1">
-      <c r="C15" s="62"/>
-      <c r="D15" s="63"/>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="40"/>
+    </row>
+    <row r="15" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="59"/>
+      <c r="D15" s="60"/>
       <c r="E15" s="13"/>
       <c r="F15" s="14"/>
       <c r="G15" s="15"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="64"/>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="45"/>
-      <c r="U15" s="46"/>
-    </row>
-    <row r="16" spans="3:22" ht="33" customHeight="1">
-      <c r="C16" s="62"/>
-      <c r="D16" s="63"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="29"/>
+    </row>
+    <row r="16" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="59"/>
+      <c r="D16" s="60"/>
       <c r="E16" s="13"/>
       <c r="F16" s="14"/>
       <c r="G16" s="15"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="64"/>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="45"/>
-      <c r="U16" s="46"/>
-    </row>
-    <row r="17" spans="3:22" ht="33" customHeight="1">
-      <c r="C17" s="62"/>
-      <c r="D17" s="63"/>
+      <c r="H16" s="88"/>
+      <c r="I16" s="88"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="105"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="29"/>
+    </row>
+    <row r="17" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="59"/>
+      <c r="D17" s="60"/>
       <c r="E17" s="13"/>
       <c r="F17" s="14"/>
       <c r="G17" s="15"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="64"/>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="45"/>
-      <c r="S17" s="45"/>
-      <c r="T17" s="45"/>
-      <c r="U17" s="46"/>
-    </row>
-    <row r="18" spans="3:22" ht="33" customHeight="1">
-      <c r="C18" s="62"/>
-      <c r="D18" s="63"/>
+      <c r="H17" s="88"/>
+      <c r="I17" s="88"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="105"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="29"/>
+    </row>
+    <row r="18" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="59"/>
+      <c r="D18" s="60"/>
       <c r="E18" s="13"/>
       <c r="F18" s="14"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="44"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="64"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="45"/>
-      <c r="S18" s="45"/>
-      <c r="T18" s="45"/>
-      <c r="U18" s="46"/>
-    </row>
-    <row r="19" spans="3:22" ht="33" customHeight="1">
-      <c r="C19" s="62"/>
-      <c r="D19" s="63"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="88"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="29"/>
+    </row>
+    <row r="19" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="59"/>
+      <c r="D19" s="60"/>
       <c r="E19" s="13"/>
       <c r="F19" s="14"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="64"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="45"/>
-      <c r="R19" s="45"/>
-      <c r="S19" s="45"/>
-      <c r="T19" s="45"/>
-      <c r="U19" s="46"/>
-    </row>
-    <row r="20" spans="3:22" ht="33" customHeight="1">
-      <c r="C20" s="62"/>
-      <c r="D20" s="63"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="105"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="29"/>
+    </row>
+    <row r="20" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="59"/>
+      <c r="D20" s="60"/>
       <c r="E20" s="13"/>
       <c r="F20" s="14"/>
       <c r="G20" s="15"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="64"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="45"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="45"/>
-      <c r="T20" s="45"/>
-      <c r="U20" s="46"/>
-    </row>
-    <row r="21" spans="3:22" ht="33" customHeight="1">
-      <c r="C21" s="62"/>
-      <c r="D21" s="63"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="29"/>
+    </row>
+    <row r="21" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="59"/>
+      <c r="D21" s="60"/>
       <c r="E21" s="13"/>
       <c r="F21" s="14"/>
       <c r="G21" s="15"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="45"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="45"/>
-      <c r="U21" s="46"/>
-    </row>
-    <row r="22" spans="3:22" ht="33" customHeight="1">
-      <c r="C22" s="62"/>
-      <c r="D22" s="63"/>
+      <c r="H21" s="88"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="29"/>
+    </row>
+    <row r="22" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="59"/>
+      <c r="D22" s="60"/>
       <c r="E22" s="13"/>
       <c r="F22" s="14"/>
       <c r="G22" s="15"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="64"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="45"/>
-      <c r="R22" s="45"/>
-      <c r="S22" s="45"/>
-      <c r="T22" s="45"/>
-      <c r="U22" s="46"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="29"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="3:22" ht="33" customHeight="1">
-      <c r="C23" s="62"/>
-      <c r="D23" s="63"/>
+    <row r="23" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="59"/>
+      <c r="D23" s="60"/>
       <c r="E23" s="13"/>
       <c r="F23" s="14"/>
       <c r="G23" s="15"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="45"/>
-      <c r="R23" s="45"/>
-      <c r="S23" s="45"/>
-      <c r="T23" s="45"/>
-      <c r="U23" s="46"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="29"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="3:22" ht="33" customHeight="1">
-      <c r="C24" s="62"/>
-      <c r="D24" s="63"/>
+    <row r="24" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="59"/>
+      <c r="D24" s="60"/>
       <c r="E24" s="13"/>
       <c r="F24" s="14"/>
       <c r="G24" s="15"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="44"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="64"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="45"/>
-      <c r="U24" s="46"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="28"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="29"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="3:22" ht="33" customHeight="1">
-      <c r="C25" s="62"/>
-      <c r="D25" s="63"/>
+    <row r="25" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="59"/>
+      <c r="D25" s="60"/>
       <c r="E25" s="13"/>
       <c r="F25" s="14"/>
       <c r="G25" s="15"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="44"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="64"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="45"/>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
-      <c r="T25" s="45"/>
-      <c r="U25" s="46"/>
+      <c r="H25" s="88"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="29"/>
       <c r="V25" s="2"/>
     </row>
-    <row r="26" spans="3:22" ht="33" customHeight="1">
-      <c r="C26" s="62"/>
-      <c r="D26" s="63"/>
+    <row r="26" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="59"/>
+      <c r="D26" s="60"/>
       <c r="E26" s="13"/>
       <c r="F26" s="14"/>
       <c r="G26" s="15"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="64"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="45"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="45"/>
-      <c r="U26" s="46"/>
+      <c r="H26" s="88"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="105"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="29"/>
       <c r="V26" s="3"/>
     </row>
-    <row r="27" spans="3:22" ht="33" customHeight="1">
-      <c r="C27" s="62"/>
-      <c r="D27" s="63"/>
+    <row r="27" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="59"/>
+      <c r="D27" s="60"/>
       <c r="E27" s="13"/>
       <c r="F27" s="14"/>
       <c r="G27" s="15"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="44"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="64"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="45"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="45"/>
-      <c r="U27" s="46"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="29"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="3:22" ht="33" customHeight="1">
-      <c r="C28" s="62"/>
-      <c r="D28" s="63"/>
+    <row r="28" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C28" s="59"/>
+      <c r="D28" s="60"/>
       <c r="E28" s="13"/>
       <c r="F28" s="14"/>
       <c r="G28" s="15"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="64"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="45"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="45"/>
-      <c r="U28" s="46"/>
+      <c r="H28" s="88"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="105"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="29"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="3:22" ht="33" customHeight="1">
-      <c r="C29" s="62"/>
-      <c r="D29" s="63"/>
+    <row r="29" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="59"/>
+      <c r="D29" s="60"/>
       <c r="E29" s="13"/>
       <c r="F29" s="14"/>
       <c r="G29" s="15"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="44"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="45"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="45"/>
-      <c r="U29" s="46"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="105"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="34"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="29"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="3:22" ht="33" customHeight="1">
-      <c r="C30" s="62"/>
-      <c r="D30" s="63"/>
+    <row r="30" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C30" s="59"/>
+      <c r="D30" s="60"/>
       <c r="E30" s="13"/>
       <c r="F30" s="14"/>
       <c r="G30" s="15"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="45"/>
-      <c r="U30" s="46"/>
+      <c r="H30" s="88"/>
+      <c r="I30" s="88"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="105"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="27"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+      <c r="U30" s="29"/>
       <c r="V30" s="2"/>
     </row>
-    <row r="31" spans="3:22" ht="33" customHeight="1">
-      <c r="C31" s="62"/>
-      <c r="D31" s="63"/>
+    <row r="31" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="59"/>
+      <c r="D31" s="60"/>
       <c r="E31" s="13"/>
       <c r="F31" s="14"/>
       <c r="G31" s="15"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="44"/>
-      <c r="M31" s="45"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="64"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="45"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="45"/>
-      <c r="U31" s="46"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="105"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="27"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="29"/>
       <c r="V31" s="3"/>
     </row>
-    <row r="32" spans="3:22" ht="33" customHeight="1">
-      <c r="C32" s="95"/>
-      <c r="D32" s="96"/>
+    <row r="32" spans="3:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="96"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="117"/>
-      <c r="M32" s="118"/>
-      <c r="N32" s="118"/>
-      <c r="O32" s="119"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="45"/>
-      <c r="U32" s="46"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="95"/>
+      <c r="J32" s="94"/>
+      <c r="K32" s="106"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="37"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="29"/>
       <c r="V32" s="3"/>
     </row>
-    <row r="33" spans="1:23" ht="33" customHeight="1">
-      <c r="C33" s="97"/>
-      <c r="D33" s="98"/>
+    <row r="33" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="57"/>
+      <c r="D33" s="58"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="117"/>
-      <c r="M33" s="118"/>
-      <c r="N33" s="118"/>
-      <c r="O33" s="119"/>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="45"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="46"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="95"/>
+      <c r="J33" s="94"/>
+      <c r="K33" s="106"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="37"/>
+      <c r="P33" s="27"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="29"/>
       <c r="V33" s="3"/>
     </row>
-    <row r="34" spans="1:23" ht="33" customHeight="1">
-      <c r="C34" s="97"/>
-      <c r="D34" s="98"/>
+    <row r="34" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="57"/>
+      <c r="D34" s="58"/>
       <c r="E34" s="8"/>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="117"/>
-      <c r="M34" s="118"/>
-      <c r="N34" s="118"/>
-      <c r="O34" s="119"/>
-      <c r="P34" s="44"/>
-      <c r="Q34" s="45"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="45"/>
-      <c r="U34" s="46"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="95"/>
+      <c r="J34" s="94"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="27"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="29"/>
       <c r="V34" s="3"/>
     </row>
-    <row r="35" spans="1:23" ht="33" customHeight="1">
-      <c r="C35" s="97"/>
-      <c r="D35" s="98"/>
+    <row r="35" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="57"/>
+      <c r="D35" s="58"/>
       <c r="E35" s="8"/>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="117"/>
-      <c r="M35" s="118"/>
-      <c r="N35" s="118"/>
-      <c r="O35" s="119"/>
-      <c r="P35" s="44"/>
-      <c r="Q35" s="45"/>
-      <c r="R35" s="45"/>
-      <c r="S35" s="45"/>
-      <c r="T35" s="45"/>
-      <c r="U35" s="46"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="95"/>
+      <c r="J35" s="94"/>
+      <c r="K35" s="106"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="36"/>
+      <c r="N35" s="36"/>
+      <c r="O35" s="37"/>
+      <c r="P35" s="27"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="29"/>
       <c r="V35" s="3"/>
     </row>
-    <row r="36" spans="1:23" ht="33" customHeight="1">
-      <c r="C36" s="32"/>
-      <c r="D36" s="33"/>
+    <row r="36" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="117"/>
+      <c r="D36" s="118"/>
       <c r="E36" s="6"/>
       <c r="F36" s="5"/>
       <c r="G36" s="19"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="37"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="117"/>
-      <c r="M36" s="118"/>
-      <c r="N36" s="118"/>
-      <c r="O36" s="119"/>
-      <c r="P36" s="44"/>
-      <c r="Q36" s="45"/>
-      <c r="R36" s="45"/>
-      <c r="S36" s="45"/>
-      <c r="T36" s="45"/>
-      <c r="U36" s="46"/>
+      <c r="H36" s="124"/>
+      <c r="I36" s="125"/>
+      <c r="J36" s="122"/>
+      <c r="K36" s="123"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="37"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="29"/>
       <c r="V36" s="3"/>
     </row>
-    <row r="37" spans="1:23" ht="33" customHeight="1">
-      <c r="C37" s="34"/>
-      <c r="D37" s="35"/>
+    <row r="37" spans="1:23" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="119"/>
+      <c r="D37" s="120"/>
       <c r="E37" s="18"/>
       <c r="F37" s="25"/>
       <c r="G37" s="10"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="38"/>
-      <c r="L37" s="117"/>
-      <c r="M37" s="118"/>
-      <c r="N37" s="118"/>
-      <c r="O37" s="119"/>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="45"/>
-      <c r="R37" s="45"/>
-      <c r="S37" s="45"/>
-      <c r="T37" s="45"/>
-      <c r="U37" s="46"/>
+      <c r="H37" s="121"/>
+      <c r="I37" s="121"/>
+      <c r="J37" s="123"/>
+      <c r="K37" s="123"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="37"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="29"/>
       <c r="V37" s="3"/>
     </row>
-    <row r="38" spans="1:23" ht="32.25" customHeight="1" thickBot="1">
-      <c r="C38" s="99" t="s">
+    <row r="38" spans="1:23" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C38" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="D38" s="100"/>
-      <c r="E38" s="100"/>
-      <c r="F38" s="100"/>
-      <c r="G38" s="101"/>
-      <c r="H38" s="102"/>
-      <c r="I38" s="103"/>
-      <c r="J38" s="116"/>
-      <c r="K38" s="116"/>
-      <c r="L38" s="122"/>
-      <c r="M38" s="123"/>
-      <c r="N38" s="123"/>
-      <c r="O38" s="125"/>
-      <c r="P38" s="122"/>
-      <c r="Q38" s="123"/>
-      <c r="R38" s="123"/>
-      <c r="S38" s="123"/>
-      <c r="T38" s="123"/>
-      <c r="U38" s="124"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="31"/>
+      <c r="N38" s="31"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="31"/>
+      <c r="R38" s="31"/>
+      <c r="S38" s="31"/>
+      <c r="T38" s="31"/>
+      <c r="U38" s="32"/>
       <c r="V38" s="4"/>
     </row>
-    <row r="39" spans="1:23" ht="7.5" customHeight="1" thickBot="1">
+    <row r="39" spans="1:23" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="22"/>
       <c r="B39" s="22"/>
       <c r="C39" s="23"/>
@@ -2905,61 +2966,196 @@
       <c r="V39" s="24"/>
       <c r="W39" s="22"/>
     </row>
-    <row r="40" spans="1:23" ht="32.25" thickBot="1">
-      <c r="C40" s="104" t="s">
+    <row r="40" spans="1:23" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C40" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="105"/>
-      <c r="E40" s="113"/>
-      <c r="F40" s="114"/>
-      <c r="G40" s="115"/>
-      <c r="H40" s="105" t="s">
+      <c r="D40" s="42"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="I40" s="108"/>
-      <c r="J40" s="110"/>
-      <c r="K40" s="111"/>
-      <c r="L40" s="111"/>
-      <c r="M40" s="111"/>
-      <c r="N40" s="111"/>
-      <c r="O40" s="111"/>
-      <c r="P40" s="111"/>
-      <c r="Q40" s="111"/>
-      <c r="R40" s="111"/>
-      <c r="S40" s="111"/>
-      <c r="T40" s="111"/>
-      <c r="U40" s="112"/>
-    </row>
-    <row r="41" spans="1:23" ht="32.25" thickBot="1">
-      <c r="C41" s="106" t="s">
+      <c r="I40" s="45"/>
+      <c r="J40" s="47"/>
+      <c r="K40" s="48"/>
+      <c r="L40" s="48"/>
+      <c r="M40" s="48"/>
+      <c r="N40" s="48"/>
+      <c r="O40" s="48"/>
+      <c r="P40" s="48"/>
+      <c r="Q40" s="48"/>
+      <c r="R40" s="48"/>
+      <c r="S40" s="48"/>
+      <c r="T40" s="48"/>
+      <c r="U40" s="49"/>
+    </row>
+    <row r="41" spans="1:23" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="D41" s="107"/>
-      <c r="E41" s="101"/>
-      <c r="F41" s="102"/>
-      <c r="G41" s="103"/>
-      <c r="H41" s="107" t="s">
+      <c r="D41" s="44"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="I41" s="109"/>
-      <c r="J41" s="110"/>
-      <c r="K41" s="111"/>
-      <c r="L41" s="111"/>
-      <c r="M41" s="111"/>
-      <c r="N41" s="111"/>
-      <c r="O41" s="111"/>
-      <c r="P41" s="111"/>
-      <c r="Q41" s="111"/>
-      <c r="R41" s="111"/>
-      <c r="S41" s="111"/>
-      <c r="T41" s="111"/>
-      <c r="U41" s="112"/>
-    </row>
-    <row r="43" spans="1:23">
+      <c r="I41" s="46"/>
+      <c r="J41" s="47"/>
+      <c r="K41" s="48"/>
+      <c r="L41" s="48"/>
+      <c r="M41" s="48"/>
+      <c r="N41" s="48"/>
+      <c r="O41" s="48"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="48"/>
+      <c r="R41" s="48"/>
+      <c r="S41" s="48"/>
+      <c r="T41" s="48"/>
+      <c r="U41" s="49"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="K43" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="159">
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="P33:U33"/>
+    <mergeCell ref="P34:U34"/>
+    <mergeCell ref="J6:U7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:U10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="P21:U21"/>
+    <mergeCell ref="P19:U19"/>
+    <mergeCell ref="P20:U20"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="L31:O31"/>
+    <mergeCell ref="C13:U13"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="L11:O11"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="L25:O25"/>
+    <mergeCell ref="L17:O17"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="G6:G12"/>
+    <mergeCell ref="H6:I7"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="P5:U5"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="L15:O15"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="P8:U8"/>
+    <mergeCell ref="P11:U11"/>
+    <mergeCell ref="P12:U12"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C6:F7"/>
+    <mergeCell ref="C9:F10"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J40:U40"/>
+    <mergeCell ref="J41:U41"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="L34:O34"/>
+    <mergeCell ref="L35:O35"/>
+    <mergeCell ref="L37:O37"/>
+    <mergeCell ref="L36:O36"/>
+    <mergeCell ref="P37:U37"/>
+    <mergeCell ref="P32:U32"/>
+    <mergeCell ref="P14:U14"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H20:I20"/>
     <mergeCell ref="C2:U4"/>
     <mergeCell ref="P35:U35"/>
     <mergeCell ref="P36:U36"/>
@@ -2984,141 +3180,6 @@
     <mergeCell ref="L28:O28"/>
     <mergeCell ref="L29:O29"/>
     <mergeCell ref="L32:O32"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="L34:O34"/>
-    <mergeCell ref="L35:O35"/>
-    <mergeCell ref="L37:O37"/>
-    <mergeCell ref="L36:O36"/>
-    <mergeCell ref="P37:U37"/>
-    <mergeCell ref="P32:U32"/>
-    <mergeCell ref="P14:U14"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J40:U40"/>
-    <mergeCell ref="J41:U41"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="P5:U5"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="L15:O15"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="P8:U8"/>
-    <mergeCell ref="P11:U11"/>
-    <mergeCell ref="P12:U12"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C6:F7"/>
-    <mergeCell ref="C9:F10"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:O12"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="G6:G12"/>
-    <mergeCell ref="H6:I7"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="L8:O8"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="L11:O11"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="L17:O17"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="P33:U33"/>
-    <mergeCell ref="P34:U34"/>
-    <mergeCell ref="J6:U7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J9:U10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="P21:U21"/>
-    <mergeCell ref="P19:U19"/>
-    <mergeCell ref="P20:U20"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="C13:U13"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H23:I23"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
